--- a/training_data_index.xlsx
+++ b/training_data_index.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Aran\predicty\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BF1F4A-7EAF-4D1C-A786-F1EDEB4F1D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet2"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="98">
   <si>
     <t>expt</t>
   </si>
@@ -304,14 +323,16 @@
     <t>distributed_cells</t>
   </si>
   <si>
-    <t>clumps_distributed_cells</t>
+    <t>mixin60</t>
+  </si>
+  <si>
+    <t>BOGUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -360,59 +381,56 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -423,10 +441,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -464,71 +482,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -556,7 +574,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -579,11 +597,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -592,13 +610,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -608,7 +626,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -617,7 +635,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -626,7 +644,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -634,10 +652,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -702,36 +720,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:T31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="11" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="12" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="14" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="14" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="14" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="12.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row r="1" spans="1:20" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -793,1689 +802,1540 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
+    <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="7">
         <v>45300</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="8">
         <v>50</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="8">
         <v>42</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="8">
         <v>10</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="8" t="s">
+      <c r="M2" s="8"/>
+      <c r="N2" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="9">
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="8">
         <v>500</v>
       </c>
-      <c r="R2" s="9">
-        <v>2</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="9">
+      <c r="R2" s="8">
+        <v>2</v>
+      </c>
+      <c r="S2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="8">
         <v>157</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
+    <row r="3" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="7">
         <v>45300</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="9">
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="8">
         <v>50</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>42</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>10</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="8" t="s">
+      <c r="M3" s="8"/>
+      <c r="N3" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="9">
+      <c r="O3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="8">
         <v>500</v>
       </c>
-      <c r="R3" s="9">
-        <v>2</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="9">
+      <c r="R3" s="8">
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="8">
         <v>134</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
+    <row r="4" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B4" s="7">
         <v>45303</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="9">
-        <v>25</v>
-      </c>
-      <c r="I4" s="9">
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="8">
+        <v>25</v>
+      </c>
+      <c r="I4" s="8">
         <v>66</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>10</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="8" t="s">
+      <c r="M4" s="8"/>
+      <c r="N4" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="9">
+      <c r="O4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="8">
         <v>500</v>
       </c>
-      <c r="R4" s="9">
-        <v>2</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T4" s="9">
+      <c r="R4" s="8">
+        <v>2</v>
+      </c>
+      <c r="S4" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" s="8">
         <v>146</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
+    <row r="5" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="7">
         <v>45303</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="9">
-        <v>25</v>
-      </c>
-      <c r="I5" s="9">
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="8">
+        <v>25</v>
+      </c>
+      <c r="I5" s="8">
         <v>66</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>10</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="8" t="s">
+      <c r="M5" s="8"/>
+      <c r="N5" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="9">
+      <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="8">
         <v>500</v>
       </c>
-      <c r="R5" s="9">
-        <v>2</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T5" s="9">
+      <c r="R5" s="8">
+        <v>2</v>
+      </c>
+      <c r="S5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T5" s="8">
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
+    <row r="6" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B6" s="7">
         <v>45307</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="9">
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="8">
         <v>24</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>24</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>3.5</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="8" t="s">
+      <c r="M6" s="8"/>
+      <c r="N6" t="s">
         <v>40</v>
       </c>
-      <c r="O6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="9">
+      <c r="O6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="8">
         <v>420</v>
       </c>
-      <c r="R6" s="9">
-        <v>2</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T6" s="9">
+      <c r="R6" s="8">
+        <v>2</v>
+      </c>
+      <c r="S6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T6" s="8">
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
+    <row r="7" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="7">
         <v>45308</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="9">
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="8">
         <v>30</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>23</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>5</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <v>1</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" t="s">
         <v>26</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q7" s="9">
+      <c r="O7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="8">
         <v>380</v>
       </c>
-      <c r="R7" s="9">
-        <v>2</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T7" s="9">
+      <c r="R7" s="8">
+        <v>2</v>
+      </c>
+      <c r="S7" t="s">
+        <v>29</v>
+      </c>
+      <c r="T7" s="8">
         <v>118</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
+    <row r="8" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="7">
         <v>45323</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="9">
-        <v>25</v>
-      </c>
-      <c r="I8" s="10">
-        <v>2.05</v>
-      </c>
-      <c r="J8" s="9">
+      <c r="H8" s="8">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="J8" s="8">
         <v>3</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8" t="s">
+      <c r="L8" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="8" t="s">
+      <c r="M8" s="8"/>
+      <c r="N8" t="s">
         <v>45</v>
       </c>
-      <c r="O8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q8" s="9">
+      <c r="O8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="8">
         <v>450</v>
       </c>
-      <c r="R8" s="10">
+      <c r="R8" s="9">
         <v>0.5</v>
       </c>
-      <c r="S8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T8" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.25">
+      <c r="S8" t="s">
+        <v>29</v>
+      </c>
+      <c r="T8" s="8"/>
+    </row>
+    <row r="9" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B9" s="7">
         <v>45328</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>115</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>20</v>
       </c>
-      <c r="J9" s="9">
-        <v>2</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="8">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
         <v>50</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" t="s">
         <v>51</v>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="8" t="s">
+      <c r="M9" s="8"/>
+      <c r="N9" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q9" s="9">
+      <c r="O9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" s="8">
         <v>310</v>
       </c>
-      <c r="R9" s="10">
-        <v>0.58</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T9" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
+      <c r="R9" s="9">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S9" t="s">
+        <v>29</v>
+      </c>
+      <c r="T9" s="8"/>
+    </row>
+    <row r="10" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="7">
         <v>45321</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="9">
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="8">
         <v>49</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>19.5</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>10</v>
       </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="8" t="s">
+      <c r="M10" s="8"/>
+      <c r="N10" t="s">
         <v>56</v>
       </c>
-      <c r="O10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" s="9">
+      <c r="O10" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="8">
         <v>400</v>
       </c>
-      <c r="R10" s="9">
-        <v>2</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T10" s="9">
+      <c r="R10" s="8">
+        <v>2</v>
+      </c>
+      <c r="S10" t="s">
+        <v>29</v>
+      </c>
+      <c r="T10" s="8">
         <v>116</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25">
+    <row r="11" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="7">
         <v>45330</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="9">
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="8">
         <v>34</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>24</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>10</v>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="8" t="s">
+      <c r="M11" s="8"/>
+      <c r="N11" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11" s="9">
+      <c r="O11" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="8">
         <v>200</v>
       </c>
-      <c r="R11" s="9">
-        <v>2</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T11" s="9">
+      <c r="R11" s="8">
+        <v>2</v>
+      </c>
+      <c r="S11" t="s">
+        <v>29</v>
+      </c>
+      <c r="T11" s="8">
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
+    <row r="12" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="7">
         <v>45335</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="9">
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="8">
         <v>30</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <v>20</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <v>10</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="8" t="s">
+      <c r="M12" s="8"/>
+      <c r="N12" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q12" s="9">
+      <c r="O12" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q12" s="8">
         <v>420</v>
       </c>
-      <c r="R12" s="9">
-        <v>2</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T12" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.25">
+      <c r="R12" s="8">
+        <v>2</v>
+      </c>
+      <c r="S12" t="s">
+        <v>29</v>
+      </c>
+      <c r="T12" s="8"/>
+    </row>
+    <row r="13" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="7">
         <v>45329</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="8">
         <v>40</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <v>23.5</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>1</v>
       </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8" t="s">
+      <c r="L13" t="s">
         <v>51</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="8" t="s">
+      <c r="M13" s="8"/>
+      <c r="N13" t="s">
         <v>52</v>
       </c>
-      <c r="O13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" s="9">
+      <c r="O13" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="8">
         <v>500</v>
       </c>
-      <c r="R13" s="9">
-        <v>2</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T13" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.25">
+      <c r="R13" s="8">
+        <v>2</v>
+      </c>
+      <c r="S13" t="s">
+        <v>29</v>
+      </c>
+      <c r="T13" s="8"/>
+    </row>
+    <row r="14" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B14" s="7">
         <v>45337</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="8">
         <v>40</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <v>22</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <v>10</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" t="s">
         <v>62</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" t="s">
         <v>51</v>
       </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="8" t="s">
+      <c r="M14" s="8"/>
+      <c r="N14" t="s">
         <v>26</v>
       </c>
-      <c r="O14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="9">
+      <c r="O14" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q14" s="8">
         <v>420</v>
       </c>
-      <c r="R14" s="9">
-        <v>2</v>
-      </c>
-      <c r="S14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T14" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
+      <c r="R14" s="8">
+        <v>2</v>
+      </c>
+      <c r="S14" t="s">
+        <v>29</v>
+      </c>
+      <c r="T14" s="8"/>
+    </row>
+    <row r="15" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B15" s="7">
         <v>45342</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="9">
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="8">
         <v>11</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>22</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <v>10</v>
       </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="8" t="s">
+      <c r="M15" s="8"/>
+      <c r="N15" t="s">
         <v>65</v>
       </c>
-      <c r="O15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q15" s="9">
+      <c r="O15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q15" s="8">
         <v>420</v>
       </c>
-      <c r="R15" s="9">
-        <v>2</v>
-      </c>
-      <c r="S15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T15" s="9">
+      <c r="R15" s="8">
+        <v>2</v>
+      </c>
+      <c r="S15" t="s">
+        <v>29</v>
+      </c>
+      <c r="T15" s="8">
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25">
+    <row r="16" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>66</v>
       </c>
       <c r="B16" s="7">
         <v>45343</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="8">
         <v>11</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <v>24</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <v>10</v>
       </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="9">
+      <c r="M16" s="8">
         <v>1</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="N16" t="s">
         <v>67</v>
       </c>
-      <c r="O16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q16" s="9">
+      <c r="O16" t="s">
+        <v>27</v>
+      </c>
+      <c r="P16" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q16" s="8">
         <v>420</v>
       </c>
-      <c r="R16" s="9">
-        <v>2</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T16" s="9">
+      <c r="R16" s="8">
+        <v>2</v>
+      </c>
+      <c r="S16" t="s">
+        <v>29</v>
+      </c>
+      <c r="T16" s="8">
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
+    <row r="17" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>68</v>
       </c>
       <c r="B17" s="7">
         <v>45344</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="9">
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="8">
         <v>80</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <v>24</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <v>10</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="8" t="s">
+      <c r="M17" s="8"/>
+      <c r="N17" t="s">
         <v>69</v>
       </c>
-      <c r="O17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="9">
+      <c r="O17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="8">
         <v>500</v>
       </c>
-      <c r="R17" s="9">
-        <v>2</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T17" s="9">
+      <c r="R17" s="8">
+        <v>2</v>
+      </c>
+      <c r="S17" t="s">
+        <v>29</v>
+      </c>
+      <c r="T17" s="8">
         <v>126</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25">
+    <row r="18" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B18" s="7">
         <v>45345</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="9">
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="8">
         <v>55</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>68</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="8">
         <v>10</v>
       </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="9">
+      <c r="M18" s="8">
         <v>38</v>
       </c>
-      <c r="N18" s="8" t="s">
+      <c r="N18" t="s">
         <v>71</v>
       </c>
-      <c r="O18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q18" s="9">
+      <c r="O18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q18" s="8">
         <v>420</v>
       </c>
-      <c r="R18" s="9">
-        <v>2</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T18" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.25">
+      <c r="R18" s="8">
+        <v>2</v>
+      </c>
+      <c r="S18" t="s">
+        <v>29</v>
+      </c>
+      <c r="T18" s="8"/>
+    </row>
+    <row r="19" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>72</v>
       </c>
       <c r="B19" s="7">
         <v>45350</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="9">
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="8">
         <v>7</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="8">
         <v>24</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="8">
         <v>10</v>
       </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="9">
+      <c r="M19" s="8">
         <v>1</v>
       </c>
-      <c r="N19" s="8" t="s">
+      <c r="N19" t="s">
         <v>74</v>
       </c>
-      <c r="O19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q19" s="9">
+      <c r="O19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q19" s="8">
         <v>420</v>
       </c>
-      <c r="R19" s="9">
-        <v>2</v>
-      </c>
-      <c r="S19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T19" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20.25">
+      <c r="R19" s="8">
+        <v>2</v>
+      </c>
+      <c r="S19" t="s">
+        <v>29</v>
+      </c>
+      <c r="T19" s="8"/>
+    </row>
+    <row r="20" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="7">
         <v>45351</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="9">
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="8">
         <v>40</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="8">
         <v>24</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="8">
         <v>1</v>
       </c>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="8" t="s">
+      <c r="M20" s="8"/>
+      <c r="N20" t="s">
         <v>77</v>
       </c>
-      <c r="O20" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" s="9">
+      <c r="O20" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" s="8">
         <v>400</v>
       </c>
-      <c r="R20" s="9">
-        <v>2</v>
-      </c>
-      <c r="S20" s="8" t="s">
+      <c r="R20" s="8">
+        <v>2</v>
+      </c>
+      <c r="S20" t="s">
         <v>78</v>
       </c>
-      <c r="T20" s="9">
+      <c r="T20" s="8">
         <v>104</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20.25">
+    <row r="21" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B21" s="7">
-        <v>45351</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="8" t="s">
+        <v>45352</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="J21" s="9">
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="8">
+        <v>240</v>
+      </c>
+      <c r="I21" s="8">
+        <v>66</v>
+      </c>
+      <c r="J21" s="8">
+        <v>10</v>
+      </c>
+      <c r="M21" s="8">
         <v>1</v>
       </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>400</v>
-      </c>
-      <c r="R21" s="9">
-        <v>2</v>
-      </c>
-      <c r="S21" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="T21" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20.25">
+      <c r="N21" t="s">
+        <v>71</v>
+      </c>
+      <c r="O21" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>420</v>
+      </c>
+      <c r="R21" s="8">
+        <v>2</v>
+      </c>
+      <c r="S21" t="s">
+        <v>29</v>
+      </c>
+      <c r="T21" s="8"/>
+    </row>
+    <row r="22" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="B22" s="7">
-        <v>45352</v>
-      </c>
-      <c r="C22" s="8" t="s">
+        <v>45354</v>
+      </c>
+      <c r="C22" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" s="9">
-        <v>240</v>
-      </c>
-      <c r="I22" s="9">
-        <v>66</v>
-      </c>
-      <c r="J22" s="9">
+      <c r="F22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="8">
+        <v>50</v>
+      </c>
+      <c r="I22" s="8">
+        <v>72</v>
+      </c>
+      <c r="J22" s="8">
         <v>10</v>
       </c>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="9">
-        <v>1</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q22" s="9">
+      <c r="M22" s="8"/>
+      <c r="N22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O22" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q22" s="8">
         <v>420</v>
       </c>
-      <c r="R22" s="9">
-        <v>2</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T22" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25">
+      <c r="R22" s="8">
+        <v>2</v>
+      </c>
+      <c r="S22" t="s">
+        <v>29</v>
+      </c>
+      <c r="T22" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B23" s="7">
         <v>45358</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="9">
-        <v>25</v>
-      </c>
-      <c r="I23" s="9">
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="8">
+        <v>25</v>
+      </c>
+      <c r="I23" s="8">
         <v>24</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="8">
         <v>10</v>
       </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="8" t="s">
+      <c r="M23" s="8"/>
+      <c r="N23" t="s">
         <v>26</v>
       </c>
-      <c r="O23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q23" s="9">
+      <c r="O23" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q23" s="8">
         <v>420</v>
       </c>
-      <c r="R23" s="9">
-        <v>2</v>
-      </c>
-      <c r="S23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T23" s="9">
+      <c r="R23" s="8">
+        <v>2</v>
+      </c>
+      <c r="S23" t="s">
+        <v>29</v>
+      </c>
+      <c r="T23" s="8">
         <v>101</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20.25">
+    <row r="24" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>82</v>
       </c>
       <c r="B24" s="7">
         <v>45359</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" t="s">
         <v>55</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="9">
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="8">
         <v>20</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="8">
         <v>67</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="8">
         <v>10</v>
       </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="8" t="s">
+      <c r="M24" s="8"/>
+      <c r="N24" t="s">
         <v>71</v>
       </c>
-      <c r="O24" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q24" s="9">
+      <c r="O24" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q24" s="8">
         <v>420</v>
       </c>
-      <c r="R24" s="9">
-        <v>2</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T24" s="9">
+      <c r="R24" s="8">
+        <v>2</v>
+      </c>
+      <c r="S24" t="s">
+        <v>29</v>
+      </c>
+      <c r="T24" s="8">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20.25">
+    <row r="25" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="7">
         <v>45372</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" t="s">
         <v>55</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" t="s">
         <v>49</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="8">
         <v>75</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="8">
         <v>24</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="9">
         <v>1.25</v>
       </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="8" t="s">
+      <c r="M25" s="8"/>
+      <c r="N25" t="s">
         <v>85</v>
       </c>
-      <c r="O25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q25" s="9">
+      <c r="O25" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q25" s="8">
         <v>250</v>
       </c>
-      <c r="R25" s="10">
+      <c r="R25" s="9">
         <v>0.75</v>
       </c>
-      <c r="S25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T25" s="9">
+      <c r="S25" t="s">
+        <v>29</v>
+      </c>
+      <c r="T25" s="8">
         <v>229</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20.25">
+    <row r="26" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>86</v>
       </c>
       <c r="B26" s="7">
         <v>45385</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" t="s">
         <v>84</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" t="s">
         <v>34</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" s="9">
+      <c r="G26" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="8">
         <f>4*60+17</f>
-      </c>
-      <c r="I26" s="10">
+        <v>257</v>
+      </c>
+      <c r="I26" s="9">
         <v>21.5</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="8">
         <v>1</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="K26" t="s">
         <v>87</v>
       </c>
-      <c r="L26" s="8" t="s">
+      <c r="L26" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="8" t="s">
+      <c r="M26" s="8"/>
+      <c r="N26" t="s">
         <v>88</v>
       </c>
-      <c r="O26" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P26" s="8" t="s">
+      <c r="O26" t="s">
+        <v>27</v>
+      </c>
+      <c r="P26" t="s">
         <v>89</v>
       </c>
-      <c r="Q26" s="9">
+      <c r="Q26" s="8">
         <v>350</v>
       </c>
-      <c r="R26" s="10">
+      <c r="R26" s="9">
         <v>1.85</v>
       </c>
-      <c r="S26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T26" s="9">
+      <c r="S26" t="s">
+        <v>29</v>
+      </c>
+      <c r="T26" s="8">
         <v>108</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25">
+    <row r="27" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>90</v>
       </c>
       <c r="B27" s="7">
         <v>45397</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" t="s">
         <v>55</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="9">
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="8">
         <v>12</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="8">
         <v>24</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="8">
         <v>10</v>
       </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="8" t="s">
+      <c r="M27" s="8"/>
+      <c r="N27" t="s">
         <v>91</v>
       </c>
-      <c r="O27" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q27" s="9">
+      <c r="O27" t="s">
+        <v>27</v>
+      </c>
+      <c r="P27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q27" s="8">
         <v>350</v>
       </c>
-      <c r="R27" s="9">
-        <v>2</v>
-      </c>
-      <c r="S27" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T27" s="9">
+      <c r="R27" s="8">
+        <v>2</v>
+      </c>
+      <c r="S27" t="s">
+        <v>29</v>
+      </c>
+      <c r="T27" s="8">
         <v>116</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20.25">
+    <row r="28" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>90</v>
       </c>
       <c r="B28" s="7">
         <v>45397</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" t="s">
         <v>55</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H28" s="9">
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="8">
         <f>24*60+32</f>
-      </c>
-      <c r="I28" s="9">
+        <v>1472</v>
+      </c>
+      <c r="I28" s="8">
         <v>23</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="8">
         <v>10</v>
       </c>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8" t="s">
+      <c r="L28" t="s">
         <v>51</v>
       </c>
-      <c r="M28" s="9"/>
-      <c r="N28" s="8" t="s">
+      <c r="M28" s="8"/>
+      <c r="N28" t="s">
         <v>92</v>
       </c>
-      <c r="O28" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q28" s="9">
+      <c r="O28" t="s">
+        <v>27</v>
+      </c>
+      <c r="P28" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q28" s="8">
         <v>350</v>
       </c>
-      <c r="R28" s="9">
-        <v>2</v>
-      </c>
-      <c r="S28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T28" s="9">
+      <c r="R28" s="8">
+        <v>2</v>
+      </c>
+      <c r="S28" t="s">
+        <v>29</v>
+      </c>
+      <c r="T28" s="8">
         <v>108</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.25">
+    <row r="29" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B29" s="7">
         <v>45411</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" t="s">
         <v>94</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" s="9">
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="8">
         <v>70</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="8">
         <v>23</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="8">
         <v>10</v>
       </c>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="8" t="s">
+      <c r="M29" s="8"/>
+      <c r="N29" t="s">
         <v>95</v>
       </c>
-      <c r="O29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q29" s="9">
+      <c r="O29" t="s">
+        <v>27</v>
+      </c>
+      <c r="P29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q29" s="8">
         <v>420</v>
       </c>
-      <c r="R29" s="9">
-        <v>2</v>
-      </c>
-      <c r="S29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T29" s="9">
+      <c r="R29" s="8">
+        <v>2</v>
+      </c>
+      <c r="S29" t="s">
+        <v>29</v>
+      </c>
+      <c r="T29" s="8">
         <v>90</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20.25">
-      <c r="A30" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="7">
-        <v>45411</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="9">
-        <f>24*60 + 20</f>
-      </c>
-      <c r="I30" s="9">
-        <v>23</v>
-      </c>
-      <c r="J30" s="9">
-        <v>10</v>
-      </c>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q30" s="9">
-        <v>420</v>
-      </c>
-      <c r="R30" s="9">
-        <v>2</v>
-      </c>
-      <c r="S30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T30" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20.25">
-      <c r="A31" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="7">
-        <v>45411</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H31" s="9">
-        <f>48*60 + 35</f>
-      </c>
-      <c r="I31" s="9">
-        <v>16</v>
-      </c>
-      <c r="J31" s="9">
-        <v>10</v>
-      </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q31" s="9">
-        <v>420</v>
-      </c>
-      <c r="R31" s="9">
-        <v>2</v>
-      </c>
-      <c r="S31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T31" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training_data_index.xlsx
+++ b/training_data_index.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Aran\predicty\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gamer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BF1F4A-7EAF-4D1C-A786-F1EDEB4F1D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3D6DB0-3E19-41F6-A026-34E9F8DF8DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="96">
   <si>
     <t>expt</t>
   </si>
@@ -321,12 +321,6 @@
   </si>
   <si>
     <t>distributed_cells</t>
-  </si>
-  <si>
-    <t>mixin60</t>
-  </si>
-  <si>
-    <t>BOGUS</t>
   </si>
 </sst>
 </file>
@@ -724,7 +718,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="10" bestFit="1" customWidth="1"/>
@@ -1896,13 +1890,13 @@
     </row>
     <row r="22" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B22" s="7">
-        <v>45354</v>
+        <v>45358</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
         <v>47</v>
@@ -1917,17 +1911,17 @@
         <v>25</v>
       </c>
       <c r="H22" s="8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I22" s="8">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="J22" s="8">
         <v>10</v>
       </c>
       <c r="M22" s="8"/>
       <c r="N22" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="O22" t="s">
         <v>27</v>
@@ -1945,18 +1939,18 @@
         <v>29</v>
       </c>
       <c r="T22" s="8">
-        <v>229</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B23" s="7">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
         <v>47</v>
@@ -1965,23 +1959,23 @@
         <v>48</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
       </c>
       <c r="H23" s="8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I23" s="8">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="J23" s="8">
         <v>10</v>
       </c>
       <c r="M23" s="8"/>
       <c r="N23" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="O23" t="s">
         <v>27</v>
@@ -1999,43 +1993,43 @@
         <v>29</v>
       </c>
       <c r="T23" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B24" s="7">
-        <v>45359</v>
+        <v>45372</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
         <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F24" t="s">
         <v>55</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="H24" s="8">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I24" s="8">
-        <v>67</v>
-      </c>
-      <c r="J24" s="8">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="J24" s="9">
+        <v>1.25</v>
       </c>
       <c r="M24" s="8"/>
       <c r="N24" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O24" t="s">
         <v>27</v>
@@ -2044,27 +2038,27 @@
         <v>28</v>
       </c>
       <c r="Q24" s="8">
-        <v>420</v>
-      </c>
-      <c r="R24" s="8">
-        <v>2</v>
+        <v>250</v>
+      </c>
+      <c r="R24" s="9">
+        <v>0.75</v>
       </c>
       <c r="S24" t="s">
         <v>29</v>
       </c>
       <c r="T24" s="8">
-        <v>102</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B25" s="7">
-        <v>45372</v>
+        <v>45385</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>47</v>
@@ -2073,49 +2067,56 @@
         <v>84</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H25" s="8">
-        <v>75</v>
-      </c>
-      <c r="I25" s="8">
-        <v>24</v>
-      </c>
-      <c r="J25" s="9">
-        <v>1.25</v>
+        <f>4*60+17</f>
+        <v>257</v>
+      </c>
+      <c r="I25" s="9">
+        <v>21.5</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
+        <v>87</v>
+      </c>
+      <c r="L25" t="s">
+        <v>51</v>
       </c>
       <c r="M25" s="8"/>
       <c r="N25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="O25" t="s">
         <v>27</v>
       </c>
       <c r="P25" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="Q25" s="8">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="R25" s="9">
-        <v>0.75</v>
+        <v>1.85</v>
       </c>
       <c r="S25" t="s">
         <v>29</v>
       </c>
       <c r="T25" s="8">
-        <v>229</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B26" s="7">
-        <v>45385</v>
+        <v>45397</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
@@ -2124,51 +2125,44 @@
         <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
       </c>
       <c r="H26" s="8">
-        <f>4*60+17</f>
-        <v>257</v>
-      </c>
-      <c r="I26" s="9">
-        <v>21.5</v>
+        <v>12</v>
+      </c>
+      <c r="I26" s="8">
+        <v>24</v>
       </c>
       <c r="J26" s="8">
-        <v>1</v>
-      </c>
-      <c r="K26" t="s">
-        <v>87</v>
-      </c>
-      <c r="L26" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="M26" s="8"/>
       <c r="N26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="O26" t="s">
         <v>27</v>
       </c>
       <c r="P26" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="Q26" s="8">
         <v>350</v>
       </c>
-      <c r="R26" s="9">
-        <v>1.85</v>
+      <c r="R26" s="8">
+        <v>2</v>
       </c>
       <c r="S26" t="s">
         <v>29</v>
       </c>
       <c r="T26" s="8">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2179,7 +2173,7 @@
         <v>45397</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
         <v>47</v>
@@ -2194,17 +2188,21 @@
         <v>25</v>
       </c>
       <c r="H27" s="8">
-        <v>12</v>
+        <f>24*60+32</f>
+        <v>1472</v>
       </c>
       <c r="I27" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J27" s="8">
         <v>10</v>
       </c>
+      <c r="L27" t="s">
+        <v>51</v>
+      </c>
       <c r="M27" s="8"/>
       <c r="N27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O27" t="s">
         <v>27</v>
@@ -2222,34 +2220,33 @@
         <v>29</v>
       </c>
       <c r="T27" s="8">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B28" s="7">
-        <v>45397</v>
+        <v>45411</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
         <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="8">
-        <f>24*60+32</f>
-        <v>1472</v>
+        <v>70</v>
       </c>
       <c r="I28" s="8">
         <v>23</v>
@@ -2257,12 +2254,9 @@
       <c r="J28" s="8">
         <v>10</v>
       </c>
-      <c r="L28" t="s">
-        <v>51</v>
-      </c>
       <c r="M28" s="8"/>
       <c r="N28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O28" t="s">
         <v>27</v>
@@ -2271,7 +2265,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="8">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="R28" s="8">
         <v>2</v>
@@ -2280,60 +2274,6 @@
         <v>29</v>
       </c>
       <c r="T28" s="8">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B29" s="7">
-        <v>45411</v>
-      </c>
-      <c r="C29" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" s="8">
-        <v>70</v>
-      </c>
-      <c r="I29" s="8">
-        <v>23</v>
-      </c>
-      <c r="J29" s="8">
-        <v>10</v>
-      </c>
-      <c r="M29" s="8"/>
-      <c r="N29" t="s">
-        <v>95</v>
-      </c>
-      <c r="O29" t="s">
-        <v>27</v>
-      </c>
-      <c r="P29" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q29" s="8">
-        <v>420</v>
-      </c>
-      <c r="R29" s="8">
-        <v>2</v>
-      </c>
-      <c r="S29" t="s">
-        <v>29</v>
-      </c>
-      <c r="T29" s="8">
         <v>90</v>
       </c>
     </row>
